--- a/insurance_data/2_care/dementia/final_monthly_dementia_comparison.xlsx
+++ b/insurance_data/2_care/dementia/final_monthly_dementia_comparison.xlsx
@@ -3159,29 +3159,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~5등급) 재가급여특약Ⅰ(표준형)</t>
+          <t>(무)경도치매보장특약Ⅰ(표준형)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>320</v>
+        <v>1213</v>
       </c>
       <c r="I2" t="n">
-        <v>514</v>
+        <v>1182</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3202,34 +3202,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(무)중증치매보장특약Ⅰ(표준형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 사망하였을 때</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="I3" t="n">
-        <v>442</v>
+        <v>270</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3255,29 +3255,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅰ(표준형)</t>
+          <t>(무)장기요양(1~5등급) 재가급여특약Ⅰ(표준형)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1213</v>
+        <v>320</v>
       </c>
       <c r="I4" t="n">
-        <v>1182</v>
+        <v>514</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3298,34 +3298,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)중증치매보장특약Ⅰ(표준형)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망하였을 때</t>
+          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="I5" t="n">
-        <v>270</v>
+        <v>442</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3394,34 +3394,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~2등급) 시설입소특약Ⅰ(해약환급금 미지급형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~2등급)”인 장기요양수급자로 시설입소급여 이용시(다만, 월1회 한도)</t>
+          <t>피보험자가 보험기간 중 사망하였을 때</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3447,29 +3447,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~5등급) 재가급여특약Ⅰ(해약환급금 미지급형)</t>
+          <t>(무)경도치매보장특약Ⅰ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>243</v>
+        <v>922</v>
       </c>
       <c r="I8" t="n">
-        <v>389</v>
+        <v>905</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3543,29 +3543,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅰ(해약환급금 미지급형)</t>
+          <t>(무)장기요양(1~5등급) 재가급여특약Ⅰ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>922</v>
+        <v>243</v>
       </c>
       <c r="I10" t="n">
-        <v>905</v>
+        <v>389</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3586,34 +3586,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)장기요양(1~2등급) 시설입소특약Ⅰ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망하였을 때</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~2등급)”인 장기요양수급자로 시설입소급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3735,12 +3735,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅰ(해약환급금 일부지급형)</t>
+          <t>(무)중증치매보장특약Ⅰ(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1093</v>
+        <v>323</v>
       </c>
       <c r="I14" t="n">
-        <v>1068</v>
+        <v>399</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -3778,34 +3778,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)경도치매보장특약Ⅰ(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망하였을 때</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>372</v>
+        <v>1093</v>
       </c>
       <c r="I15" t="n">
-        <v>248</v>
+        <v>1068</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -3826,34 +3826,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(무)중증치매보장특약Ⅰ(해약환급금 일부지급형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 사망하였을 때</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>323</v>
+        <v>372</v>
       </c>
       <c r="I16" t="n">
-        <v>399</v>
+        <v>248</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -3874,34 +3874,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~2등급) 시설입소특약Ⅱ(표준형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~2등급)”인 장기요양수급자로 시설입소급여 이용시(다만, 월1회 한도)</t>
+          <t>피보험자가 보험기간 중 사망하였을 때</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>38</v>
+        <v>408</v>
       </c>
       <c r="I17" t="n">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -3927,29 +3927,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~5등급) 재가급여특약Ⅱ(표준형)</t>
+          <t>(무)경도치매보장특약Ⅱ(표준형)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>457</v>
+        <v>1772</v>
       </c>
       <c r="I18" t="n">
-        <v>619</v>
+        <v>1416</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4023,29 +4023,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅱ(표준형)</t>
+          <t>(무)장기요양(1~5등급) 재가급여특약Ⅱ(표준형)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1772</v>
+        <v>457</v>
       </c>
       <c r="I20" t="n">
-        <v>1416</v>
+        <v>619</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -4066,34 +4066,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)장기요양(1~2등급) 시설입소특약Ⅱ(표준형)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망하였을 때</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~2등급)”인 장기요양수급자로 시설입소급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="I21" t="n">
-        <v>270</v>
+        <v>65</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -4162,34 +4162,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)장기요양(1~5등급) 재가급여특약Ⅱ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망하였을 때</t>
+          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원(이용 1회당)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="I23" t="n">
-        <v>210</v>
+        <v>469</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅱ(해약환급금 미지급형)</t>
+          <t>(무)중증치매보장특약Ⅱ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1342</v>
+        <v>438</v>
       </c>
       <c r="I24" t="n">
-        <v>1080</v>
+        <v>420</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -4258,34 +4258,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(무)중증치매보장특약Ⅱ(해약환급금 미지급형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 사망하였을 때</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>438</v>
+        <v>322</v>
       </c>
       <c r="I25" t="n">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -4311,29 +4311,29 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(무)장기요양(1~5등급) 재가급여특약Ⅱ(해약환급금 미지급형)</t>
+          <t>(무)경도치매보장특약Ⅱ(해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>장기요양상태보장개시일 이후 피보험자가 “장기요양상태(1~5등급)”인 장기요양수급자로 재가급여 이용시(다만, 월1회 한도)</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10만원(이용 1회당)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>347</v>
+        <v>1342</v>
       </c>
       <c r="I26" t="n">
-        <v>469</v>
+        <v>1080</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(무)경도치매보장특약Ⅱ(해약환급금 일부지급형)</t>
+          <t>(무)중증치매보장특약Ⅱ(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1599</v>
+        <v>527</v>
       </c>
       <c r="I29" t="n">
-        <v>1278</v>
+        <v>503</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(무)중증치매보장특약Ⅱ(해약환급금 일부지급형)</t>
+          <t>(무)경도치매보장특약Ⅱ(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “경도이상 치매상태”로 진단 확정되었을 경우(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>527</v>
+        <v>1599</v>
       </c>
       <c r="I30" t="n">
-        <v>503</v>
+        <v>1278</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -4599,17 +4599,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>중등도이상치매 간병생활자금</t>
+          <t>중증치매 진단급여금</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
+          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>매월 중등도이상치매 간병생활자금 지급해당일: 200만원(60회확정지급)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4647,17 +4647,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>중증치매 간병생활자금</t>
+          <t>중등도이상치매 진단급여금</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
+          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>매월 중증치매 간병생활자금 지급해당일: 200만원(60회확정지급)</t>
+          <t>700만원</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>중등도이상치매 진단급여금</t>
+          <t>경도이상치매 진단급여금</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
+          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>700만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>중증치매 진단급여금</t>
+          <t>중증치매 간병생활자금</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>매월 중증치매 간병생활자금 지급해당일: 200만원(60회확정지급)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>경도이상치매 진단급여금</t>
+          <t>중등도이상치매 간병생활자금</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
+          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>매월 중등도이상치매 간병생활자금 지급해당일: 200만원(60회확정지급)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5067,15 +5067,15 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>중등증이상치매진단비(납입완료체증형)(5년질문추가)(간편고지)</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>중증치매진단비(납입완료체증형)(5년질문추가)(간편고지)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -5099,17 +5099,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>중등치매진단자금(매월5년간지급)(납입완료체증형)(5년질문추가)(간편고지)</t>
+          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(납입완료체증형)(5년질문추가)(간편고지)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>보험가입금액(100만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+          <t>보험가입금액(10만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5135,13 +5135,17 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>중증치매진단비(납입완료체증형)(5년질문추가)(간편고지)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>중등치매진단자금(매월5년간지급)(납입완료체증형)(5년질문추가)(간편고지)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+          <t>보험가입금액(100만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5167,19 +5171,15 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(납입완료체증형)(5년질문추가)(간편고지)</t>
+          <t>중등증이상치매진단비(납입완료체증형)(5년질문추가)(간편고지)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>보험가입금액(10만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -5799,12 +5799,12 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -5831,12 +5831,12 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -6015,19 +6015,15 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(무사고체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -6051,12 +6047,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(무사고체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -6083,15 +6079,19 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(무사고체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -6163,12 +6163,12 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(무사고연장형)(요양간편고지)</t>
+          <t>보험료납입면제대상보장Ⅱ(4대질병)(요양간편고지)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 요양보장개시일(보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암보장개시일(보험계약일로부터 그 날을 포함하여 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -6195,15 +6195,19 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(무사고연장형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(무사고연장형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -6227,19 +6231,15 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(무사고연장형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(무사고연장형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -6263,12 +6263,12 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>보험료납입면제대상보장Ⅱ(4대질병)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(무사고연장형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 요양보장개시일(보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암보장개시일(보험계약일로부터 그 날을 포함하여 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -6343,19 +6343,15 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(요양간편고지)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -6379,12 +6375,12 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~3등급)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(요양간편고지)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급 또는 3등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -6411,12 +6407,12 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~3등급)(요양간편고지)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급 또는 3등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -6443,15 +6439,19 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(요양간편고지)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -6523,19 +6523,15 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
@@ -6559,12 +6555,12 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~3등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급 또는 3등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -6591,12 +6587,12 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~3등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급 또는 3등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -6623,15 +6619,19 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(납입완료체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(납입완료체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
@@ -6703,17 +6703,17 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(무사고체증형)(요양간편고지)</t>
+          <t>체증불가대상보장(4대질병)(요양간편고지)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
+          <t>보험가입금액(10만원)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -6739,12 +6739,12 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(무사고체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~5등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -6771,12 +6771,12 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(무사고체증형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -6803,17 +6803,17 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>체증불가대상보장(4대질병)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(무사고체증형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>보험가입금액(10만원)</t>
+          <t>보험가입금액(1,000만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -6887,15 +6887,19 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>보험료납입면제대상보장Ⅱ(4대질병)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~2등급)(무사고연장형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 요양보장개시일(보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암보장개시일(보험계약일로부터 그 날을 포함하여 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
@@ -6919,19 +6923,15 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~2등급)(무사고연장형)(요양간편고지)</t>
+          <t>장기간병요양진단비(1~4등급)(무사고연장형)(요양간편고지)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(무사고연장형)(요양간편고지)</t>
+          <t>보험료납입면제대상보장Ⅱ(4대질병)(요양간편고지)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 보장개시일 이후에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우(보장개시일 : 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날)</t>
+          <t>피보험자가 이 특별약관의 보험기간 중 아래의 어느 하나에 해당하는 사고를 당한 경우 최초 1회에 한하여 지급. 다만, 어떠한 경우에도 중복하여 지급하지 않습니다.   ① 요양보장개시일(보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 「노인장기요양보험 수급대상(1~3급)」으로 인정되었을 경우   ② 암보장개시일(보험계약일로부터 그 날을 포함하여 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정된 경우   ③ 뇌졸중으로 진단이 확정된 경우   ④ 급성심근경색증으로 진단이 확정된 경우</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -7067,25 +7067,21 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>중등치매진단자금(매월5년간지급)</t>
+          <t>중등증이상치매진단비</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>보험가입금액(100만원)</t>
-        </is>
-      </c>
+          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>월납(연납환산, 5년납)</t>
+          <t>월납(연납환산, 20년납)</t>
         </is>
       </c>
     </row>
@@ -7103,13 +7099,17 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>중증치매진단비</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>보험가입금액(1,000만원)</t>
+          <t>보험가입금액(10만원)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -7135,17 +7135,17 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)</t>
+          <t>중등치매진단자금(매월5년간지급)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>보험가입금액(10만원)</t>
+          <t>보험가입금액(100만원)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -7153,7 +7153,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>월납(연납환산, 20년납)</t>
+          <t>월납(연납환산, 5년납)</t>
         </is>
       </c>
     </row>
@@ -7171,15 +7171,15 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>중등증이상치매진단비</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>중증치매진단비</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>보험가입금액(1,000만원)</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
@@ -7251,15 +7251,19 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>중등증이상치매진단비(납입완료체증형)</t>
+          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(납입완료체증형)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>보험가입금액(10만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
@@ -7283,17 +7287,13 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>중등치매진단자금(매월5년간지급)(납입완료체증형)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
+          <t>중증치매진단비(납입완료체증형)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>보험가입금액(100만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>월납(연납환산, 5년납)</t>
+          <t>월납(연납환산, 20년납)</t>
         </is>
       </c>
     </row>
@@ -7319,15 +7319,15 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>중증치매진단비(납입완료체증형)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>보험가입금액(1,000만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
-        </is>
-      </c>
+          <t>중등증이상치매진단비(납입완료체증형)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
@@ -7351,17 +7351,17 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(납입완료체증형)</t>
+          <t>중등치매진단자금(매월5년간지급)(납입완료체증형)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
+          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>보험가입금액(10만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
+          <t>보험가입금액(100만원)단, 납입기간 경과 후 보험금 지급사유 발생시 가입급액의 200% 지급</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -7369,7 +7369,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>월납(연납환산, 20년납)</t>
+          <t>월납(연납환산, 5년납)</t>
         </is>
       </c>
     </row>
@@ -7435,15 +7435,19 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>중등증이상치매진단비(무사고체증형)</t>
+          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(무사고체증형)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>보험가입금액(10만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -7467,12 +7471,12 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>중증치매진단비(무사고체증형)</t>
+          <t>중등증이상치매진단비(무사고체증형)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+          <t>피보험자가 해당 특별약관 중등증이상치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 진단확정된 질병 또는 상해로 인해 중등증이상 인지기능의 장애(CDR척도 2점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -7499,15 +7503,15 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>체증불가대상보장(중증치매)</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>보험가입금액(10만원)</t>
-        </is>
-      </c>
+          <t>중증치매진단비(무사고체증형)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>피보험자가 해당 특별약관 보험기간 중 진단확정된 질병 또는 상해로 인해 중증인지기능의 장애(CDR척도 3점이상에 해당하는 상태가 90일이상 계속되어 더 이상의 호전을 기대할 수 없는 상태)가 발생한 상태로 진단확정된 경우</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -7531,17 +7535,13 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>치매전문재활치료비(급여)(1일1회한)(연간10회한)(무사고체증형)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>피보험자가 해당 특별약관 치매보장개시일(질병으로 인한 치매의 경우 보험계약일로부터 그 날을 포함하여 1년이 지난날의 다음날) 이후에 치매로 진단확정되고 그 치매의 직접적인 치료를 목적으로 치매전문재활치료를 받은 경우</t>
-        </is>
-      </c>
+          <t>체증불가대상보장(중증치매)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>보험가입금액(10만원)단, 85세 계약해당일 전일 이전에 체증불가사유가 발생하지 않은 경우, 85세 이후 보험금 지급사유 발생시 가입금액의 200% 지급</t>
+          <t>보험가입금액(10만원)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -8347,10 +8347,14 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>보험료납입면제대상보장(4대질병)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>장기간병요양진단비(1~5등급)(무사고연장형)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>피보험자가 해당 특별약관 보험기간 중에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
@@ -8411,14 +8415,10 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~4등급)(무사고연장형)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>피보험자가 해당 특별약관 보험기간 중에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우</t>
-        </is>
-      </c>
+          <t>보험료납입면제대상보장(4대질병)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
@@ -8443,12 +8443,12 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>장기간병요양진단비(1~5등급)(무사고연장형)</t>
+          <t>장기간병요양진단비(1~4등급)(무사고연장형)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>피보험자가 해당 특별약관 보험기간 중에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급, 4등급 또는 5등급의 장기요양등급 판정을 받은 경우</t>
+          <t>피보험자가 해당 특별약관 보험기간 중에 노인장기요양보험 수급대상으로 인정되어 국민건강보험 등급판정위원회에 의해 1등급, 2등급, 3등급 또는 4등급의 장기요양등급 판정을 받은 경우</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -8479,17 +8479,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>중증치매진단비</t>
+          <t>중등도이상치매간병비</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중증치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중등도이상치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>매월 100만원 * 84회 확정지급</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8527,17 +8527,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비</t>
+          <t>중증치매간병비</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중등도이상치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중증치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>매월 100만원 * 84회 확정지급</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8623,17 +8623,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>중증치매간병비</t>
+          <t>중등도이상치매진단비</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중증치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중등도이상치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>매월 100만원 * 84회 확정지급</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>중등도이상치매간병비</t>
+          <t>중증치매진단비</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중등도이상치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일”이후에 “중증치매상태”로 최종 진단확정되었을 때 (최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>매월 100만원 * 84회 확정지급</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8714,34 +8714,34 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>표적치매약물허가치료비특약(최경도,경도알츠)36회한도(갱,무)_TW</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망한 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 '치매보장개시일' 이후에 '최경도치매상태' 또는 '경도알츠하이머치매상태'로 진단확정 되고, '아밀로이드베타 적응증 상태'로 판정 받은 후 '최경도치매상태' 또는 '경도알츠하이머치매상태'의 직접적인 치료를 목적으로 '아밀로이드베타 표적약물허가치료제'의 투약 또는 투여를 받았을 때</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1,000 만원</t>
+          <t>"1회당 90만원 (최대 36회한)"</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1,000 만원</t>
+          <t>900만원</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>21000</v>
+        <v>18</v>
       </c>
       <c r="I142" t="n">
-        <v>18400</v>
+        <v>63</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -8767,17 +8767,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>급여치매검사비특약(해약일부지급,무)_DW</t>
+          <t>급여치매치료제ㆍ통원특약(해약일부지급,무)_DW</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 '급여치매CTㆍMRI보장개시일' 이후에 '치매'의 진단 및 치료를 위한 필요 소견을 토대로 '급여치매CTㆍMRI촬영'을 받았을 때(다만, 연간 1회 한도)</t>
+          <t>*급여치매치료자금 : 피보험자가 이 특약의 보험기간 중 '치매보장개시일' 이후에 '급여치매치료제'를 처방 받았을 때(다만, 연간 1회 한도) *종합병원치매통원급여금 : 피보험자가 이 특약의 보험기간 중 '치매보장개시일'이후에 '치매'로 진단이 확정되고, 그 '치매'의 치료를 직접 목적으로 종합병원에 통원하였을 때(통원 1회당, 1일 1회한, 연간 30회한)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1회당 10만원</t>
+          <t>*급여치매치료자금 : 1회당 20만원 *종합병원치매통원급여금 : 1회당 5만원</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>98</v>
+        <v>2190</v>
       </c>
       <c r="I143" t="n">
-        <v>154</v>
+        <v>3930</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -8815,17 +8815,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>급여치매치료제ㆍ통원특약(해약일부지급,무)_DW</t>
+          <t>"치매생활자금특약(해약일부지급,무)_DW 2종(종합형)"</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>*급여치매치료자금 : 피보험자가 이 특약의 보험기간 중 '치매보장개시일' 이후에 '급여치매치료제'를 처방 받았을 때(다만, 연간 1회 한도) *종합병원치매통원급여금 : 피보험자가 이 특약의 보험기간 중 '치매보장개시일'이후에 '치매'로 진단이 확정되고, 그 '치매'의 치료를 직접 목적으로 종합병원에 통원하였을 때(통원 1회당, 1일 1회한, 연간 30회한)</t>
+          <t>* 중증치매간병생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일'이후에 '중증치매상태'로 진단확정 되고, '중증치매 진단 확정일'부터 매년 '중증치매 진단확정일'에 살아있을 때 (다만, '중증치매상태' 진단확정은 최초 1회에 한함) * 중증도이상 치매간병 생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일' 이후에 '중증도이상치매상태'로 진단확정되고, '중증도이상치매진단확정일'부터 매년 '중증도이상치매 진단확정일'에 살아있을 때 (다만, '중증도이상치매상태' 진단확정은 최초 1회에 한함) * 경도이상치매간병생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일' 이후에 '경도이상치매상태'로 진단확정되고, '경도이상치매 진단확정일'부터 매년 '경도이상치매 진단확정일'에 살아있을 때 (다만, '경도이상치매상태' 진단확정은 최초 1회에 한함) * 유지보너스 : 피보험자가 이 특약(세부보장)의 보험료 납입기간 중 '치매간병 생활자금'의 지급사유가 발생하지 않고 '유지보너스' 지급시기(보험료 납입 기간 경과시점의 연계약해당일)에 살아있을 때 (1회한)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>*급여치매치료자금 : 1회당 20만원 *종합병원치매통원급여금 : 1회당 5만원</t>
+          <t>* 중증치매간병생활자금 : 매월 60만원(최대종신지급) * 중증도이상치매간병생활자금 : 매월 30만원(최대종신지급) * 경도이상치매간병생활자금 : 매월 10만원(최대10년지급) * 유지보너스 : 계약자가 납입한 이 특약(세부보장)의 총 납입보험료 x 8%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>2190</v>
+        <v>31500</v>
       </c>
       <c r="I144" t="n">
-        <v>3930</v>
+        <v>44300</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -8858,34 +8858,34 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>표적치매약물허가치료비특약(최경도,경도알츠)36회한도(갱,무)_TW</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 '치매보장개시일' 이후에 '최경도치매상태' 또는 '경도알츠하이머치매상태'로 진단확정 되고, '아밀로이드베타 적응증 상태'로 판정 받은 후 '최경도치매상태' 또는 '경도알츠하이머치매상태'의 직접적인 치료를 목적으로 '아밀로이드베타 표적약물허가치료제'의 투약 또는 투여를 받았을 때</t>
+          <t>피보험자가 보험기간 중 사망한 경우</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>"1회당 90만원 (최대 36회한)"</t>
+          <t>1,000 만원</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>900만원</t>
+          <t>1,000 만원</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>18</v>
+        <v>21000</v>
       </c>
       <c r="I145" t="n">
-        <v>63</v>
+        <v>18400</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>"치매생활자금특약(해약일부지급,무)_DW 2종(종합형)"</t>
+          <t>급여치매검사비특약(해약일부지급,무)_DW</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>* 중증치매간병생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일'이후에 '중증치매상태'로 진단확정 되고, '중증치매 진단 확정일'부터 매년 '중증치매 진단확정일'에 살아있을 때 (다만, '중증치매상태' 진단확정은 최초 1회에 한함) * 중증도이상 치매간병 생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일' 이후에 '중증도이상치매상태'로 진단확정되고, '중증도이상치매진단확정일'부터 매년 '중증도이상치매 진단확정일'에 살아있을 때 (다만, '중증도이상치매상태' 진단확정은 최초 1회에 한함) * 경도이상치매간병생활자금 : 피보험자가 이 세부보장의 보험기간 중 '치매보장개시일' 이후에 '경도이상치매상태'로 진단확정되고, '경도이상치매 진단확정일'부터 매년 '경도이상치매 진단확정일'에 살아있을 때 (다만, '경도이상치매상태' 진단확정은 최초 1회에 한함) * 유지보너스 : 피보험자가 이 특약(세부보장)의 보험료 납입기간 중 '치매간병 생활자금'의 지급사유가 발생하지 않고 '유지보너스' 지급시기(보험료 납입 기간 경과시점의 연계약해당일)에 살아있을 때 (1회한)</t>
+          <t>피보험자가 이 특약의 보험기간 중 '급여치매CTㆍMRI보장개시일' 이후에 '치매'의 진단 및 치료를 위한 필요 소견을 토대로 '급여치매CTㆍMRI촬영'을 받았을 때(다만, 연간 1회 한도)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>* 중증치매간병생활자금 : 매월 60만원(최대종신지급) * 중증도이상치매간병생활자금 : 매월 30만원(최대종신지급) * 경도이상치매간병생활자금 : 매월 10만원(최대10년지급) * 유지보너스 : 계약자가 납입한 이 특약(세부보장)의 총 납입보험료 x 8%</t>
+          <t>1회당 10만원</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>31500</v>
+        <v>98</v>
       </c>
       <c r="I146" t="n">
-        <v>44300</v>
+        <v>154</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -8959,17 +8959,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>중증치매 생활비</t>
+          <t>중등도치매 진단자금</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중증치매상태”로 최종 진단확정 받은 때(60개월 확정지급)(최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중등도치매상태"로 최종 진단확정 받은 때(최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>매월 중증치매 생활비 지급해당일 1회~36회 : 200만원 37회~60회 : 100만원</t>
+          <t>1,000만원 (다만, “경도치매 진단자금”이 지급된 후에 “중등도치매상태”로 최종 진단확정시 상기금액에서 “경도치매 진단자금”을 뺀 차액을 지급)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9007,17 +9007,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>중등도이상치매 생활비</t>
+          <t>중증치매 생활비</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중등도이상치매상태"로 최종 진단확정 받은 때(60개월 확정지급)(최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중증치매상태”로 최종 진단확정 받은 때(60개월 확정지급)(최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>매월 중등도이상치매 생활비 지급해당일 1회~60회 : 70만원</t>
+          <t>매월 중증치매 생활비 지급해당일 1회~36회 : 200만원 37회~60회 : 100만원</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>중증치매 진단자금</t>
+          <t>중등도이상치매 생활비</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중증치매상태"로 최종 진단확정 받은 때(최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중등도이상치매상태"로 최종 진단확정 받은 때(60개월 확정지급)(최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2,000만원 (다만, “경도치매 진단자금” 또는 “중등도치매 진단자금”이 지급된 후에 “중증치매상태”로 최종 진단확정시 상기금액에서 이미 지급받은 진단자금의 총 합계액을 뺀 차액을 지급)</t>
+          <t>매월 중등도이상치매 생활비 지급해당일 1회~60회 : 70만원</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9103,17 +9103,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>중등도치매 진단자금</t>
+          <t>중증치매 진단자금</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중등도치매상태"로 최종 진단확정 받은 때(최초 1회에 한함)</t>
+          <t>피보험자가 보험기간 중 "치매보장개시일" 이후에 "중증치매상태"로 최종 진단확정 받은 때(최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1,000만원 (다만, “경도치매 진단자금”이 지급된 후에 “중등도치매상태”로 최종 진단확정시 상기금액에서 “경도치매 진단자금”을 뺀 차액을 지급)</t>
+          <t>2,000만원 (다만, “경도치매 진단자금” 또는 “중등도치매 진단자금”이 지급된 후에 “중증치매상태”로 최종 진단확정시 상기금액에서 이미 지급받은 진단자금의 총 합계액을 뺀 차액을 지급)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>무배당 장기요양진단특약L(1~인지지원등급)(간편N355)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~인지지원등급) 보장개시일” 이후에 최초로 “장기요양상태(1~인지지원등급)”가 되었을 경우(다만, 최초 1회의 판정에 한함)</t>
+          <t>보험기간 중 피보험자가 사망하였을 경우</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>보험가입금액(다만, 계약일로부터 2년 미만에 재 해 이외의 원인으로 사망하였을 경우 보험가입금액의 50%)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>1680</v>
+        <v>21200</v>
       </c>
       <c r="I157" t="n">
-        <v>2130</v>
+        <v>19000</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>무배당 장기요양진단특약L(1~인지지원등급)(간편N355)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 사망하였을 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~인지지원등급) 보장개시일” 이후에 최초로 “장기요양상태(1~인지지원등급)”가 되었을 경우(다만, 최초 1회의 판정에 한함)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>보험가입금액(다만, 계약일로부터 2년 미만에 재 해 이외의 원인으로 사망하였을 경우 보험가입금액의 50%)</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>21200</v>
+        <v>1680</v>
       </c>
       <c r="I158" t="n">
-        <v>19000</v>
+        <v>2130</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -10154,22 +10154,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>무배당 장기요양재가급여특약L(1~5등급)(각1일,복지용구제외)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 사망하였을 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~5등급) 보장개시일” 이후에 최초로 “장기요양상태(1~5등급)”가 되고 “재가급여” 중 방문요양을 이용하는 경우(다만, “장기요양등급(1~5등급) 판정일”로부터 10년을 최고 한도로 하여 지급, 1일1회에 한함) ※ 이외 보장담보는 상품요약서 참조</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>보험가입금액</t>
+          <t>이용 1회당 1만원</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>21100</v>
+        <v>9450</v>
       </c>
       <c r="I172" t="n">
-        <v>18900</v>
+        <v>14430</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -10202,22 +10202,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>무배당 장기요양진단특약L(1~인지지원등급)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~인지지원등급) 보장개시일” 이후에 최초로 “장기요양상태(1~인지지원등급)”가 되었을 경우(다만, 최초 1회의 판정에 한함)</t>
+          <t>보험기간 중 피보험자가 사망하였을 경우</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>보험가입금액</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1560</v>
+        <v>21100</v>
       </c>
       <c r="I173" t="n">
-        <v>2020</v>
+        <v>18900</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -10255,17 +10255,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>무배당 장기요양재가급여특약L(1~5등급)(각1일,복지용구제외)</t>
+          <t>무배당 장기요양진단특약L(1~인지지원등급)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~5등급) 보장개시일” 이후에 최초로 “장기요양상태(1~5등급)”가 되고 “재가급여” 중 방문요양을 이용하는 경우(다만, “장기요양등급(1~5등급) 판정일”로부터 10년을 최고 한도로 하여 지급, 1일1회에 한함) ※ 이외 보장담보는 상품요약서 참조</t>
+          <t>피보험자가 이 특약의 보험기간 중 “장기요양상태(1~인지지원등급) 보장개시일” 이후에 최초로 “장기요양상태(1~인지지원등급)”가 되었을 경우(다만, 최초 1회의 판정에 한함)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>이용 1회당 1만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>9450</v>
+        <v>1560</v>
       </c>
       <c r="I174" t="n">
-        <v>14430</v>
+        <v>2020</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -10443,12 +10443,12 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>중증치매진단비</t>
+          <t>중등도이상치매진단비</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
@@ -10507,12 +10507,12 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비</t>
+          <t>중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -10539,12 +10539,12 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비</t>
+          <t>중증치매진단비</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -10619,12 +10619,12 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>간편가입중증치매진단비</t>
+          <t>간편가입경증이상치매진단비</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 경증이상치매로 진단 확정되고 그 시점부터 경증이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR1이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -10651,12 +10651,12 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>간편가입중증알츠하이머치매진단비</t>
+          <t>간편가입중등도이상치매진단비</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -10683,12 +10683,12 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>간편가입중등도이상치매진단비</t>
+          <t>간편가입중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
@@ -10715,12 +10715,12 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>간편가입경증이상치매진단비</t>
+          <t>간편가입중증치매진단비</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 경증이상치매로 진단 확정되고 그 시점부터 경증이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR1이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
@@ -10795,12 +10795,12 @@
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>중증치매진단비</t>
+          <t>경증이상치매진단비</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 경증이상치매로 진단 확정되고 그 시점부터 경증이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR1이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
@@ -10827,12 +10827,12 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비</t>
+          <t>중등도이상치매진단비</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
@@ -10859,12 +10859,12 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비</t>
+          <t>중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중등도이상치매로 진단 확정되고 그 시점부터 중등도이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR2이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F190" t="inlineStr"/>
@@ -10891,12 +10891,12 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>경증이상치매진단비</t>
+          <t>중증치매진단비</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 경증이상치매로 진단 확정되고 그 시점부터 경증이상치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR1이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -11035,12 +11035,12 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>간편가입중증치매진단비</t>
+          <t>간편가입중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F195" t="inlineStr"/>
@@ -11067,12 +11067,12 @@
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>간편가입중증알츠하이머치매진단비</t>
+          <t>간편가입중증치매진단비</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증알츠하이머치매로 진단 확정되고 그 시점부터 중증알츠하이머치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
+          <t>치매보장개시일 이후 진단확정된 질병 또는 상해로 인하여 중증치매로 진단 확정되고 그 시점부터 중증치매상태가 90일이상 계속되어 인지기능의 장애가 발생한 경우(CDR3이상)＊치매보장개시일 : 계약일부터 그날을 포함하여 1년이 지난날의 다음날. 단, 치매상태가 없는 상태에서 상해로 뇌의 손상을 직접적인 원인으로 치매상태가 발생한 경우 계약일(갱신형 계약의 경우 최초 계약일)을 치매보장개시일로 합니다.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
@@ -11199,17 +11199,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>경도이상 치매진단비</t>
+          <t>다발경화증 진단비</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 다발경화증으로 진단확정 되었을 때 (최초 1회한)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -11247,17 +11247,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>중증치매 간병비</t>
+          <t>루게릭병 진단비</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 루게릭병으로 진단확정 되었을 때 (최초 1회한)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>매월 중증치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
+          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11343,17 +11343,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>루게릭병 진단비</t>
+          <t>중증치매 간병비</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 루게릭병으로 진단확정 되었을 때 (최초 1회한)</t>
+          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
+          <t>매월 중증치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -11391,17 +11391,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>다발경화증 진단비</t>
+          <t>경도이상 치매진단비</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 다발경화증으로 진단확정 되었을 때 (최초 1회한)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -11439,17 +11439,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>중증치매 진단비</t>
+          <t>경도이상 치매진단비</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>300만원</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11487,17 +11487,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>중등도이상 치매진단비</t>
+          <t>다발경화증 진단비</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 다발경화증으로 진단확정 되었을 때 (최초 1회한)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>700만원</t>
+          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11535,17 +11535,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>경도이상 치매진단비</t>
+          <t>루게릭병 진단비</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “경도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 루게릭병으로 진단확정 되었을 때 (최초 1회한)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>300만원</t>
+          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11583,17 +11583,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>중증치매 간병비</t>
+          <t>중등도이상 치매간병비</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>매월 중증치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
+          <t>매월 중등도이상치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11631,17 +11631,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비</t>
+          <t>중증치매 간병비</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
+          <t>피보험자가 보험기간 중 “치매 보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>매월 중등도이상치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
+          <t>매월 중증치매간병비 지급해당일: 100만원 (84회 확정지급)</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>루게릭병 진단비</t>
+          <t>중등도이상 치매진단비</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 루게릭병으로 진단확정 되었을 때 (최초 1회한)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
+          <t>700만원</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -11727,17 +11727,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>다발경화증 진단비</t>
+          <t>중증치매 진단비</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 다발경화증으로 진단확정 되었을 때 (최초 1회한)</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중증치매상태”로 진단확정 되었을 때 (최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>1,000만원 (다만, 계약일부터 1년미만 진단확정시 50% 지급)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -11770,34 +11770,34 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>무배당시니어수술보장특약D</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>백내장으로 진단확정되고, 그 치료를 직접적인 목적으로 수술분류표에서 정한 수술을 받았을 때(수술 1회당) ‘※ 이외 보장담보는 상품요약서 참조’</t>
+          <t>사망하였을 경우</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>보험가입금액의 3%</t>
+          <t>보험가입금액</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="H211" t="n">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="I211" t="n">
-        <v>473</v>
+        <v>180</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -11823,12 +11823,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>무배당중증치매보장특약D</t>
+          <t>무배당경도이상치매보장특약D</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>424</v>
+        <v>1220</v>
       </c>
       <c r="I212" t="n">
-        <v>609</v>
+        <v>1389</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -11914,34 +11914,34 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>무배당중증치매보장특약D</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>사망하였을 경우</t>
+          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>보험가입금액</t>
+          <t>보험가입금액(면책 1년)</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H214" t="n">
-        <v>206</v>
+        <v>424</v>
       </c>
       <c r="I214" t="n">
-        <v>180</v>
+        <v>609</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>무배당경도이상치매보장특약D</t>
+          <t>무배당시니어수술보장특약D</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
+          <t>백내장으로 진단확정되고, 그 치료를 직접적인 목적으로 수술분류표에서 정한 수술을 받았을 때(수술 1회당) ‘※ 이외 보장담보는 상품요약서 참조’</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>보험가입금액(면책 1년)</t>
+          <t>보험가입금액의 3%</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -11986,10 +11986,10 @@
         </is>
       </c>
       <c r="H215" t="n">
-        <v>1220</v>
+        <v>245</v>
       </c>
       <c r="I215" t="n">
-        <v>1389</v>
+        <v>473</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -12015,17 +12015,17 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>무배당경도이상치매보장특약D</t>
+          <t>무배당시니어수술보장특약D</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
+          <t>백내장으로 진단확정되고, 그 치료를 직접적인 목적으로 수술분류표에서 정한 수술을 받았을 때(수술 1회당) ‘※ 이외 보장담보는 상품요약서 참조’</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>보험가입금액(면책 1년)</t>
+          <t>보험가입금액의 3%</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>1002</v>
+        <v>188</v>
       </c>
       <c r="I216" t="n">
-        <v>1143</v>
+        <v>357</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -12058,34 +12058,34 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>무배당중등도이상치매보장특약D</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
+          <t>사망하였을 경우</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>보험가입금액(면책 1년)</t>
+          <t>보험가입금액</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="H217" t="n">
-        <v>654</v>
+        <v>178</v>
       </c>
       <c r="I217" t="n">
-        <v>795</v>
+        <v>154</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>무배당중증치매보장특약D</t>
+          <t>무배당경도이상치매보장특약D</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
+          <t>“치매보장개시일” 이후에 “경도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>345</v>
+        <v>1002</v>
       </c>
       <c r="I218" t="n">
-        <v>496</v>
+        <v>1143</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>무배당시니어수술보장특약D</t>
+          <t>무배당중등도이상치매보장특약D</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>백내장으로 진단확정되고, 그 치료를 직접적인 목적으로 수술분류표에서 정한 수술을 받았을 때(수술 1회당) ‘※ 이외 보장담보는 상품요약서 참조’</t>
+          <t>“치매보장개시일” 이후에 “중등도이상치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>보험가입금액의 3%</t>
+          <t>보험가입금액(면책 1년)</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>188</v>
+        <v>654</v>
       </c>
       <c r="I219" t="n">
-        <v>357</v>
+        <v>795</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -12202,34 +12202,34 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>무배당중증치매보장특약D</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>사망하였을 경우</t>
+          <t>“치매보장개시일” 이후에 “중증치매상태”로 진단확정되었을 때(다만, 최초 1회에 한함)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>보험가입금액</t>
+          <t>보험가입금액(면책 1년)</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H220" t="n">
-        <v>178</v>
+        <v>345</v>
       </c>
       <c r="I220" t="n">
-        <v>154</v>
+        <v>496</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>무배당시설급여보장특약(기본형)</t>
+          <t>무배당장기요양(1~2등급)시설급여보장특약(기본형)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 장기요양 1~2등급으로 인한 시설급여를 이용하였을 때 (장기요양 1~2등급으로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12514,10 +12514,10 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>2500</v>
+        <v>790</v>
       </c>
       <c r="I226" t="n">
-        <v>4760</v>
+        <v>1460</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -12538,34 +12538,34 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>중증치매간병생활자금</t>
+          <t>무배당집에서집중간병특약(기본형)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 중증치매로 진단 확정되고 진단확정일을 최초로 하여 매년 중증치매 진단확정일에 살아있을 경우 (최초 36회 보증지급, 최대 종신 지급)</t>
+          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>매월 100만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>1000만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H227" t="n">
-        <v>52200</v>
+        <v>9900</v>
       </c>
       <c r="I227" t="n">
-        <v>42200</v>
+        <v>13700</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -12591,29 +12591,29 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>무배당경도이상치매플러스진단특약(기본형)</t>
+          <t>무배당시설급여보장특약(기본형)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
+          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
           <t>1,000만원</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>1,000만원</t>
-        </is>
-      </c>
       <c r="H228" t="n">
-        <v>31900</v>
+        <v>2500</v>
       </c>
       <c r="I228" t="n">
-        <v>26700</v>
+        <v>4760</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -12639,17 +12639,17 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>무배당장기요양(1~2등급)시설급여보장특약(기본형)</t>
+          <t>무배당경도이상치매플러스진단특약(기본형)</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양 1~2등급으로 인한 시설급여를 이용하였을 때 (장기요양 1~2등급으로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>790</v>
+        <v>31900</v>
       </c>
       <c r="I229" t="n">
-        <v>1460</v>
+        <v>26700</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -12682,34 +12682,34 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>무배당집에서집중간병특약(기본형)</t>
+          <t>중증치매간병생활자금</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 중증치매로 진단 확정되고 진단확정일을 최초로 하여 매년 중증치매 진단확정일에 살아있을 경우 (최초 36회 보증지급, 최대 종신 지급)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>매월 100만원</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>1000만원</t>
         </is>
       </c>
       <c r="H230" t="n">
-        <v>9900</v>
+        <v>52200</v>
       </c>
       <c r="I230" t="n">
-        <v>13700</v>
+        <v>42200</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -12783,29 +12783,29 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>무배당경도이상치매플러스진단특약(해약환급금미지급형)</t>
+          <t>무배당집에서집중간병특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
+          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
           <t>1,000만원</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>1,000만원</t>
-        </is>
-      </c>
       <c r="H232" t="n">
-        <v>23000</v>
+        <v>7400</v>
       </c>
       <c r="I232" t="n">
-        <v>19400</v>
+        <v>10100</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>무배당시설급여보장특약(해약환급금미지급형)</t>
+          <t>무배당장기요양(1~2등급)시설급여보장특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 장기요양 1~2등급으로 인한 시설급여를 이용하였을 때 (장기요양 1~2등급으로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="H233" t="n">
-        <v>1850</v>
+        <v>600</v>
       </c>
       <c r="I233" t="n">
-        <v>3460</v>
+        <v>1080</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -12879,12 +12879,12 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>무배당장기요양(1~2등급)시설급여보장특약(해약환급금미지급형)</t>
+          <t>무배당시설급여보장특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양 1~2등급으로 인한 시설급여를 이용하였을 때 (장기요양 1~2등급으로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12898,10 +12898,10 @@
         </is>
       </c>
       <c r="H234" t="n">
-        <v>600</v>
+        <v>1850</v>
       </c>
       <c r="I234" t="n">
-        <v>1080</v>
+        <v>3460</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -12927,17 +12927,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>무배당집에서집중간병특약(해약환급금미지급형)</t>
+          <t>무배당경도이상치매플러스진단특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -12946,10 +12946,10 @@
         </is>
       </c>
       <c r="H235" t="n">
-        <v>7400</v>
+        <v>23000</v>
       </c>
       <c r="I235" t="n">
-        <v>10100</v>
+        <v>19400</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -12970,22 +12970,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>치매 재가급여 지원금</t>
+          <t>무배당경도이상치매플러스진단특약(기본형)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "치매"로 진단 확정되고 "치매로 인한 재가급여"를 이용하였을 때</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -12994,10 +12994,10 @@
         </is>
       </c>
       <c r="H236" t="n">
-        <v>5500</v>
+        <v>31900</v>
       </c>
       <c r="I236" t="n">
-        <v>7500</v>
+        <v>26700</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -13018,34 +13018,34 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>무배당경도이상치매플러스진단특약(기본형)</t>
+          <t>치매 재가급여 지원금</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 경도이상치매로 진단확정되었을 때 (다만, 최초 1회에 한하여 지급함) ※ 이외 보장 담보는 상품요약서 참조</t>
+          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "치매"로 진단 확정되고 "치매로 인한 재가급여"를 이용하였을 때</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
           <t>1,000만원</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>1,000만원</t>
-        </is>
-      </c>
       <c r="H237" t="n">
-        <v>31900</v>
+        <v>5500</v>
       </c>
       <c r="I237" t="n">
-        <v>26700</v>
+        <v>7500</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -13210,17 +13210,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>무배당시설급여보장특약(해약환급금미지급형)</t>
+          <t>치매 재가급여 지원금</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "치매"로 진단 확정되고 "치매로 인한 재가급여"를 이용하였을 때</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13234,10 +13234,10 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="I241" t="n">
-        <v>3460</v>
+        <v>5600</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -13263,12 +13263,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>무배당중증치매시설급여보장특약(해약환급금미지급형)</t>
+          <t>무배당집에서집중간병특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "중증치매"로 진단 확정되고 중증치매로 인한 시설급여를 이용하였을 때 (중증치매로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13282,10 +13282,10 @@
         </is>
       </c>
       <c r="H242" t="n">
-        <v>550</v>
+        <v>7400</v>
       </c>
       <c r="I242" t="n">
-        <v>950</v>
+        <v>10100</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -13359,12 +13359,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>무배당집에서집중간병특약(해약환급금미지급형)</t>
+          <t>무배당중증치매시설급여보장특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 재가급여 보장개시일 이후에 재가급여를 이용하였을 때 (재가급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
+          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "중증치매"로 진단 확정되고 중증치매로 인한 시설급여를 이용하였을 때 (중증치매로 인한 시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="H244" t="n">
-        <v>7400</v>
+        <v>550</v>
       </c>
       <c r="I244" t="n">
-        <v>10100</v>
+        <v>950</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -13402,17 +13402,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>치매 재가급여 지원금</t>
+          <t>무배당시설급여보장특약(해약환급금미지급형)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매간병 보장개시일 이후에 "치매"로 진단 확정되고 "치매로 인한 재가급여"를 이용하였을 때</t>
+          <t>피보험자가 보험기간 중 시설급여를 이용하였을 때 (시설급여 이용 1회당 지급하며, 월 1회 한도로 지급함)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="H245" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="I245" t="n">
-        <v>5600</v>
+        <v>3460</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -13499,19 +13499,15 @@
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>장기요양자금(1,2등급)[일반심사형/간편심사형Ⅶ]</t>
+          <t>장기요양자금(1~4등급)[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>국민건강보험공단 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1등급 또는 2등급)으로 인정된 경우</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>① 상해로 인한 인정시 : 보험가입금액② 질병으로 인한 인정시 : 보험가입금액(단, 계약일로부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
-        </is>
-      </c>
+          <t>국민건강보험공단 등급판정위원회에 의해 '1~4등급'의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1~4등급)으로 인정된 경우</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
@@ -13535,15 +13531,19 @@
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>중증치매진단비[일반심사형/간편심사형Ⅶ]</t>
+          <t>장기요양자금(1,2등급)[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>중증치매상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr"/>
+          <t>국민건강보험공단 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1등급 또는 2등급)으로 인정된 경우</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>① 상해로 인한 인정시 : 보험가입금액② 질병으로 인한 인정시 : 보험가입금액(단, 계약일로부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
@@ -13603,12 +13603,12 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>장기요양자금(1~4등급)[일반심사형/간편심사형Ⅶ]</t>
+          <t>중증치매진단비[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>국민건강보험공단 등급판정위원회에 의해 '1~4등급'의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1~4등급)으로 인정된 경우</t>
+          <t>중증치매상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
@@ -13683,15 +13683,19 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>중증치매진단비[일반심사형/간편심사형Ⅶ]</t>
+          <t>장기요양자금(1,2등급)[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>중증치매상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
+          <t>국민건강보험공단 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1등급 또는 2등급)으로 인정된 경우</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>① 상해로 인한 인정시 : 보험가입금액② 질병으로 인한 인정시 : 보험가입금액(단, 계약일로부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
@@ -13715,19 +13719,15 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비[일반심사형/간편심사형Ⅶ]</t>
+          <t>장기요양자금(1~4등급)[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>중등도이상치매상태로 진단확정된 경우</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>보험가입금액</t>
-        </is>
-      </c>
+          <t>국민건강보험공단 등급판정위원회에 의해 '1~4등급'의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1~4등급)으로 인정된 경우</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
@@ -13751,12 +13751,12 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>장기요양자금(1~4등급)[일반심사형/간편심사형Ⅶ]</t>
+          <t>중증치매진단비[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>국민건강보험공단 등급판정위원회에 의해 '1~4등급'의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1~4등급)으로 인정된 경우</t>
+          <t>중증치매상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -13783,17 +13783,17 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>장기요양자금(1,2등급)[일반심사형/간편심사형Ⅶ]</t>
+          <t>중등도이상치매진단비[일반심사형/간편심사형Ⅶ]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>국민건강보험공단 등급판정위원회에 의해 1등급 또는 2등급의 장기요양등급을 판정받아 노인장기요양보험 수급대상(1등급 또는 2등급)으로 인정된 경우</t>
+          <t>중등도이상치매상태로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>① 상해로 인한 인정시 : 보험가입금액② 질병으로 인한 인정시 : 보험가입금액(단, 계약일로부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+          <t>보험가입금액</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
@@ -14051,17 +14051,17 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>중증치매간병비(간편가입)</t>
+          <t>신골절치료비(치아파절포함)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
+          <t>「신골절」로 진단확정시</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>11,000만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G262" t="inlineStr"/>
@@ -14087,17 +14087,17 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비(간편가입)</t>
+          <t>중증치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>11,000만원</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
@@ -14123,17 +14123,17 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>일반상해80%이상후유장해</t>
+          <t>중등도이상 치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G264" t="inlineStr"/>
@@ -14159,17 +14159,17 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>신골절치료비(치아파절포함)</t>
+          <t>일반상해80%이상후유장해</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>「신골절」로 진단확정시</t>
+          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
@@ -14435,17 +14435,17 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>중증치매간병비(간편가입)</t>
+          <t>일반상해80%이상후유장해</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
+          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>11,000만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="G272" t="inlineStr"/>
@@ -14471,17 +14471,17 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비(간편가입)</t>
+          <t>중증치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>11,000만원</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
@@ -14507,17 +14507,17 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>일반상해80%이상후유장해</t>
+          <t>중등도이상 치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G274" t="inlineStr"/>
@@ -14627,17 +14627,17 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비(간편가입)</t>
+          <t>중증치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>11,000만원</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
@@ -14663,17 +14663,17 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>일반상해80%이상후유장해</t>
+          <t>중등도이상 치매간병비(간편가입)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G278" t="inlineStr"/>
@@ -14699,17 +14699,17 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>신골절치료비(치아파절포함)</t>
+          <t>일반상해80%이상후유장해</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>「신골절」로 진단확정시</t>
+          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
@@ -14735,17 +14735,17 @@
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>중증치매간병비(간편가입)</t>
+          <t>신골절치료비(치아파절포함)</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
+          <t>「신골절」로 진단확정시</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>11,000만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
@@ -14819,17 +14819,17 @@
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>신골절치료비(치아파절포함)</t>
+          <t>중증치매간병비</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>「신골절」로 진단확정시</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>11,000만원</t>
         </is>
       </c>
       <c r="G282" t="inlineStr"/>
@@ -14855,17 +14855,17 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>일반상해80%이상후유장해</t>
+          <t>중등도이상 치매간병비</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
@@ -14891,17 +14891,17 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비</t>
+          <t>일반상해80%이상후유장해</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
+          <t>상해에서 정한 장해지급률이 80%이상에 해당하는 장해상태가 되었을 때</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
@@ -14927,17 +14927,17 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>중증치매간병비</t>
+          <t>신골절치료비(치아파절포함)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
+          <t>「신골절」로 진단확정시</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>11,000만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
@@ -15203,17 +15203,17 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>중등도이상 치매간병비</t>
+          <t>중증치매간병비</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2,000만원</t>
+          <t>11,000만원</t>
         </is>
       </c>
       <c r="G292" t="inlineStr"/>
@@ -15239,17 +15239,17 @@
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>중증치매간병비</t>
+          <t>중등도이상 치매간병비</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>보험기간 중 진단확정된 질병 또는 상해로 「중증치매상태」로 진단확정되었을 때</t>
+          <t>보험기간 중 진단확정된 질병 또는 상해로 중등도이상 치매 보장개시일 이후에 「중등도이상 치매상태」로 진단확정되었을 때</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>11,000만원</t>
+          <t>2,000만원</t>
         </is>
       </c>
       <c r="G293" t="inlineStr"/>
@@ -15538,34 +15538,34 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>무배당 중등도이상치매간병생활자금특약(무해약환급금형)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 사망하였을 때</t>
+          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중등도이상 치매상태”로 진단 확정되고, 진단확정일부터 매년 진단확정일에 살아있을 경우 (최초 36회(3년) 보증지급, 최대 15년(180회) 지급)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>매월 25만원</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>25만원</t>
         </is>
       </c>
       <c r="H301" t="n">
-        <v>2498</v>
+        <v>21500</v>
       </c>
       <c r="I301" t="n">
-        <v>2154</v>
+        <v>25000</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -15591,29 +15591,29 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>무배당 중증치매진단특약(무해약환급금형)</t>
+          <t>무배당 중증치매간병생활자금특약(무해약환급금형)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “중증치매상태”로 진 단 확정되었을 때 (다만, 최초 1 회에 한하여 지급)</t>
+          <t>피보험자가 보험기간 중 “중증치매상태”로 진단 확정되고, 진단확정일부터 매년 진단확정일에 살아있을 경우 (최초 36회(3년) 보증지급, 최대 20년(240회) 지급)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>500만원</t>
+          <t>매월 25만원</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>500만원</t>
+          <t>25만원</t>
         </is>
       </c>
       <c r="H302" t="n">
-        <v>3960</v>
+        <v>10000</v>
       </c>
       <c r="I302" t="n">
-        <v>4450</v>
+        <v>13250</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -15687,29 +15687,29 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>무배당 중증치매간병생활자금특약(무해약환급금형)</t>
+          <t>무배당 중증치매진단특약(무해약환급금형)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “중증치매상태”로 진단 확정되고, 진단확정일부터 매년 진단확정일에 살아있을 경우 (최초 36회(3년) 보증지급, 최대 20년(240회) 지급)</t>
+          <t>피보험자가 보험기간 중 “중증치매상태”로 진 단 확정되었을 때 (다만, 최초 1 회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>매월 25만원</t>
+          <t>500만원</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>25만원</t>
+          <t>500만원</t>
         </is>
       </c>
       <c r="H304" t="n">
-        <v>10000</v>
+        <v>3960</v>
       </c>
       <c r="I304" t="n">
-        <v>13250</v>
+        <v>4450</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -15730,34 +15730,34 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>무배당 중등도이상치매간병생활자금특약(무해약환급금형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 “치매보장개시일” 이후에 “중등도이상 치매상태”로 진단 확정되고, 진단확정일부터 매년 진단확정일에 살아있을 경우 (최초 36회(3년) 보증지급, 최대 15년(180회) 지급)</t>
+          <t>보험기간 중 피보험자가 사망하였을 때</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>매월 25만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>25만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="H305" t="n">
-        <v>21500</v>
+        <v>2498</v>
       </c>
       <c r="I305" t="n">
-        <v>25000</v>
+        <v>2154</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -15778,22 +15778,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>치매진단특약(중등도이상) 간편고지형(355) [기본형]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망한 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
+          <t>이 특약 보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -15802,10 +15802,10 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>18180</v>
+        <v>11480</v>
       </c>
       <c r="I306" t="n">
-        <v>10860</v>
+        <v>12660</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -15831,12 +15831,12 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>치매진단특약(경도이상) 간편고지형(355) [기본형]</t>
+          <t>치매진단특약(중증) 간편고지형(355) [기본형]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -15850,10 +15850,10 @@
         </is>
       </c>
       <c r="H307" t="n">
-        <v>17820</v>
+        <v>5290</v>
       </c>
       <c r="I307" t="n">
-        <v>18840</v>
+        <v>7040</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -15879,29 +15879,29 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>치매진단특약(중등도이상) 간편고지형(355) [기본형]</t>
+          <t>치매진단특약(경도이상) 월지급형 간편고지형(355) [기본형]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일이후에 ‘경도이상치매상태’로 최종 진단확정되고, 매년 ‘경도이상치매상태’ 최종 진단확정일에 살아있을 경우(월 1회한)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>이 특약 보험가입금액의 100%</t>
+          <t>1회 지급금액 : 이 특약 보험가입금액의 100% / 총 지급액 : 이 특약 보험가입금액의 100%를 매년 경도이상치매상태 최종 진단확정일에 생존하는 경우 매월 경도이상치매상태 최종 진단확정일에 지급 (최초 36회 확정지급하며 최대 120회 지급)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H308" t="n">
-        <v>11480</v>
+        <v>11682</v>
       </c>
       <c r="I308" t="n">
-        <v>12660</v>
+        <v>13872</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -15927,29 +15927,29 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>치매진단특약(경도이상) 월지급형 간편고지형(355) [기본형]</t>
+          <t>치매진단특약(경도이상) 간편고지형(355) [기본형]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일이후에 ‘경도이상치매상태’로 최종 진단확정되고, 매년 ‘경도이상치매상태’ 최종 진단확정일에 살아있을 경우(월 1회한)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>1회 지급금액 : 이 특약 보험가입금액의 100% / 총 지급액 : 이 특약 보험가입금액의 100%를 매년 경도이상치매상태 최종 진단확정일에 생존하는 경우 매월 경도이상치매상태 최종 진단확정일에 지급 (최초 36회 확정지급하며 최대 120회 지급)</t>
+          <t>이 특약 보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H309" t="n">
-        <v>11682</v>
+        <v>17820</v>
       </c>
       <c r="I309" t="n">
-        <v>13872</v>
+        <v>18840</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -15970,22 +15970,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>치매진단특약(중증) 간편고지형(355) [기본형]</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 보험기간 중 사망한 경우</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>이 특약 보험가입금액의 100%</t>
+          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -15994,10 +15994,10 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>5290</v>
+        <v>18180</v>
       </c>
       <c r="I310" t="n">
-        <v>7040</v>
+        <v>10860</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -16018,22 +16018,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>치매진단특약(경도이상) 일반가입형 [기본형]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망한 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
+          <t>이 특약 보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -16042,10 +16042,10 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>25500</v>
+        <v>17750</v>
       </c>
       <c r="I311" t="n">
-        <v>22270</v>
+        <v>19790</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -16071,29 +16071,29 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>치매진단특약(경도이상) 일반가입형 [기본형]</t>
+          <t>치매진단특약(경도이상) 월지급형 일반가입형 [기본형]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일이후에 ‘경도이상치매상태’로 최종 진단확정되고, 매년 ‘경도이상치매상태’ 최종 진단확정일에 살아있을 경우(월 1회한)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>이 특약 보험가입금액의 100%</t>
+          <t>1회 지급금액 : 이 특약 보험가입금액의 100% / 총 지급액 : 이 특약 보험가입금액의 100%를 매년 경도이상치매상태 최종 진단확정일에 생존하는 경우 매월 경도이상치매상태 최종 진단확정일에 지급 (최초 36회 확정지급하며 최대 120회 지급)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H312" t="n">
-        <v>17750</v>
+        <v>11164</v>
       </c>
       <c r="I312" t="n">
-        <v>19790</v>
+        <v>13395</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -16119,29 +16119,29 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>치매진단특약(경도이상) 월지급형 일반가입형 [기본형]</t>
+          <t>치매진단특약(중등도이상) 일반가입형 [기본형]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일이후에 ‘경도이상치매상태’로 최종 진단확정되고, 매년 ‘경도이상치매상태’ 최종 진단확정일에 살아있을 경우(월 1회한)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>1회 지급금액 : 이 특약 보험가입금액의 100% / 총 지급액 : 이 특약 보험가입금액의 100%를 매년 경도이상치매상태 최종 진단확정일에 생존하는 경우 매월 경도이상치매상태 최종 진단확정일에 지급 (최초 36회 확정지급하며 최대 120회 지급)</t>
+          <t>이 특약 보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H313" t="n">
-        <v>11164</v>
+        <v>12150</v>
       </c>
       <c r="I313" t="n">
-        <v>13395</v>
+        <v>14530</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -16167,12 +16167,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>치매진단특약(중등도이상) 일반가입형 [기본형]</t>
+          <t>치매진단특약(중증) 일반가입형 [기본형]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -16186,10 +16186,10 @@
         </is>
       </c>
       <c r="H314" t="n">
-        <v>12150</v>
+        <v>6540</v>
       </c>
       <c r="I314" t="n">
-        <v>14530</v>
+        <v>9390</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -16210,22 +16210,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>치매진단특약(중증) 일반가입형 [기본형]</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 보험기간 중 사망한 경우</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>이 특약 보험가입금액의 100%</t>
+          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -16234,10 +16234,10 @@
         </is>
       </c>
       <c r="H315" t="n">
-        <v>6540</v>
+        <v>25500</v>
       </c>
       <c r="I315" t="n">
-        <v>9390</v>
+        <v>22270</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -16258,22 +16258,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>치매진단특약(중증) 일반가입형 [해약환급금이 없는 유형]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 사망한 경우</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
+          <t>이 특약 보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -16282,10 +16282,10 @@
         </is>
       </c>
       <c r="H316" t="n">
-        <v>20270</v>
+        <v>4640</v>
       </c>
       <c r="I316" t="n">
-        <v>17360</v>
+        <v>6640</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -16311,12 +16311,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>치매진단특약(경도이상) 일반가입형 [해약환급금이 없는 유형]</t>
+          <t>치매진단특약(중등도이상) 일반가입형 [해약환급금이 없는 유형]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -16330,10 +16330,10 @@
         </is>
       </c>
       <c r="H317" t="n">
-        <v>12730</v>
+        <v>8660</v>
       </c>
       <c r="I317" t="n">
-        <v>14170</v>
+        <v>10340</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -16402,22 +16402,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>치매진단특약(중등도이상) 일반가입형 [해약환급금이 없는 유형]</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중등도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 보험기간 중 사망한 경우</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>이 특약 보험가입금액의 100%</t>
+          <t>보험가입금액 ※ 보험기간 중 피보험자에게 사망보험금 지급사유가 발생한 경우에는 해당 보험금과 ""이미 납입한보험료"" 중 큰 금액을 지급합니다</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -16426,10 +16426,10 @@
         </is>
       </c>
       <c r="H319" t="n">
-        <v>8660</v>
+        <v>20270</v>
       </c>
       <c r="I319" t="n">
-        <v>10340</v>
+        <v>17360</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -16455,12 +16455,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>치매진단특약(중증) 일반가입형 [해약환급금이 없는 유형]</t>
+          <t>치매진단특약(경도이상) 일반가입형 [해약환급금이 없는 유형]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 중증치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
+          <t>피보험자가 이 특약의 보험기간 중 치매보장개시일 이후 경도이상치매상태로 최종 진단확정 되었을 경우 (다만, 최초 1회에 한하여 지급)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -16474,10 +16474,10 @@
         </is>
       </c>
       <c r="H320" t="n">
-        <v>4640</v>
+        <v>12730</v>
       </c>
       <c r="I320" t="n">
-        <v>6640</v>
+        <v>14170</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -16551,17 +16551,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>중등도치매진단급여금</t>
+          <t>중증치매진단급여금</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 "치매보장개시일" 이후에 "중증치매진단급여금" 지급사유 발생없이 "중등도치매상태"로 최종 진단확정되었을 때 (다만, 최초 1회의 진단확정에 한함)</t>
+          <t>보험기간 중 피보험자가 "치매보장개시일" 이후에 "중증치매상태"로 최종 진단확정되었을 때 (다만, 최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>보험가입금액의 150% - 이미 지급된 경증치매진단급여금</t>
+          <t>보험가입금액의 300% - 이미 지급된 경증 및 중등도치매진단급여금</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -16599,17 +16599,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>중증치매진단급여금</t>
+          <t>중등도치매진단급여금</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 "치매보장개시일" 이후에 "중증치매상태"로 최종 진단확정되었을 때 (다만, 최초 1회의 진단확정에 한함)</t>
+          <t>보험기간 중 피보험자가 "치매보장개시일" 이후에 "중증치매진단급여금" 지급사유 발생없이 "중등도치매상태"로 최종 진단확정되었을 때 (다만, 최초 1회의 진단확정에 한함)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>보험가입금액의 300% - 이미 지급된 경증 및 중등도치매진단급여금</t>
+          <t>보험가입금액의 150% - 이미 지급된 경증치매진단급여금</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -16791,12 +16791,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)방문요양보장특약(무배당, 해약환급금 미지급형)</t>
+          <t>장기요양(1-인지지원등급)복지용구보장특약 (무배당, 해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~5등급) 상태”로 판정되고, 이후 피보험자가 특약보험 기간 중에 “방문요양”을 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
+          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~인지지원등급) 상태”로 판정되고, 이후 피보험자가 특약보험기간 중에 “복지용구”를 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -16810,10 +16810,10 @@
         </is>
       </c>
       <c r="H327" t="n">
-        <v>4180</v>
+        <v>2150</v>
       </c>
       <c r="I327" t="n">
-        <v>6620</v>
+        <v>3380</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -16887,12 +16887,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>장기요양(1-인지지원등급)복지용구보장특약 (무배당, 해약환급금 미지급형)</t>
+          <t>장기요양(1-5등급)방문요양보장특약(무배당, 해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~인지지원등급) 상태”로 판정되고, 이후 피보험자가 특약보험기간 중에 “복지용구”를 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
+          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~5등급) 상태”로 판정되고, 이후 피보험자가 특약보험 기간 중에 “방문요양”을 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -16906,10 +16906,10 @@
         </is>
       </c>
       <c r="H329" t="n">
-        <v>2150</v>
+        <v>4180</v>
       </c>
       <c r="I329" t="n">
-        <v>3380</v>
+        <v>6620</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -17122,34 +17122,34 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>장기요양(1-5등급)방문요양보장특약(무배당, 해약환급금 미지급형)</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 사망하였을 때</t>
+          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~5등급) 상태”로 판정되고, 이후 피보험자가 특약보험 기간 중에 “방문요양”을 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>보험가입금액의 100%</t>
+          <t>【 이용 1회당 】 특약보험가입금액의 1%</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>400만원</t>
+          <t>1000만원</t>
         </is>
       </c>
       <c r="H334" t="n">
-        <v>7740</v>
+        <v>4180</v>
       </c>
       <c r="I334" t="n">
-        <v>5832</v>
+        <v>6620</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -17218,34 +17218,34 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)방문요양보장특약(무배당, 해약환급금 미지급형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>특약보험기간 중 피보험자가 “장기요양상태 보장개시일” 이후에 “장기요양(1~5등급) 상태”로 판정되고, 이후 피보험자가 특약보험 기간 중에 “방문요양”을 이용하였을 때 (다만, “판정후 보험월” 기준 월1회에 한함)</t>
+          <t>보험기간 중 피보험자가 사망하였을 때</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>【 이용 1회당 】 특약보험가입금액의 1%</t>
+          <t>보험가입금액의 100%</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>1000만원</t>
+          <t>400만원</t>
         </is>
       </c>
       <c r="H336" t="n">
-        <v>4180</v>
+        <v>7740</v>
       </c>
       <c r="I336" t="n">
-        <v>6620</v>
+        <v>5832</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -17319,17 +17319,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>중증치매 진단자금</t>
+          <t>중등도이상치매 간병비</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중증치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중등도이상치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>매월 150만원(84회 확정지급)</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -17367,17 +17367,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>중등도이상치매 진단자금</t>
+          <t>중증치매 간병비</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중등도이상치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중증치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>매월 150만원(84회 확정지급)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -17463,17 +17463,17 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>중증치매 간병비</t>
+          <t>중등도이상치매 진단자금</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중증치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중등도이상치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>매월 150만원(84회 확정지급)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -17511,17 +17511,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>중등도이상치매 간병비</t>
+          <t>중증치매 진단자금</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중등도이상치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
+          <t>피보험자가 보험기간 중 치매보장개시일 이후에 ‘중증치매상태’로 최종 진단이 확정되었을 때(최초 1 회에 한함)</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>매월 150만원(84회 확정지급)</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -17603,12 +17603,12 @@
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~2급)</t>
+          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -17635,12 +17635,12 @@
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
+          <t>간편고지(3.2.5) 중등도이상치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -17699,12 +17699,12 @@
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 중등도이상치매진단비Ⅱ</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -17731,12 +17731,12 @@
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~2급)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -17811,12 +17811,12 @@
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
+          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -17843,12 +17843,12 @@
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~2급)</t>
+          <t>간편고지(3.2.5) 중등도이상치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -17907,12 +17907,12 @@
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 중등도이상치매진단비Ⅱ</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -17939,12 +17939,12 @@
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~2급)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -18051,12 +18051,12 @@
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
+          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -18115,12 +18115,12 @@
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 중증치매진단비Ⅱ</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~인지지원등급)</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -18147,12 +18147,12 @@
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>간편고지(3.2.5) 장기요양진단비(1~인지지원등급)</t>
+          <t>간편고지(3.2.5) 장기요양진단비(1~5급)</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -18435,12 +18435,12 @@
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>중증치매진단비Ⅱ</t>
+          <t>장기요양진단비(1~2급)</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -18467,12 +18467,12 @@
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~2급)</t>
+          <t>장기요양진단비(1~5급)</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -18499,12 +18499,12 @@
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~5급)</t>
+          <t>장기요양진단비(1~인지지원등급)</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -18531,12 +18531,12 @@
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~인지지원등급)</t>
+          <t>중등도이상치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -18563,12 +18563,12 @@
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비Ⅱ</t>
+          <t>중증치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -18643,12 +18643,12 @@
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~5급)</t>
+          <t>중증치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -18675,12 +18675,12 @@
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~인지지원등급)</t>
+          <t>장기요양진단비(1~2급)</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -18707,12 +18707,12 @@
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비Ⅱ</t>
+          <t>장기요양진단비(1~5급)</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~5급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
@@ -18739,12 +18739,12 @@
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>중증치매진단비Ⅱ</t>
+          <t>장기요양진단비(1~인지지원등급)</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중증치매상태로 진단 확정된 경우</t>
+          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~인지지원등급) 수급대상으로 인정되었을 경우</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
@@ -18771,12 +18771,12 @@
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>장기요양진단비(1~2급)</t>
+          <t>중등도이상치매진단비Ⅱ</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>장기요양 보장개시일 이후에  노인장기요양보험(1~2급) 수급대상으로 인정되었을 경우</t>
+          <t>치매보장개시일 이후에 질병 또는 상해로 인하여 중등도이상치매상태로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F378" t="inlineStr"/>
@@ -18807,29 +18807,29 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)시설급여특약(월1회) 무배당</t>
+          <t>장기요양(1-5등급)재가급여특약(월1회) 무배당</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘재가급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
+          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘시설급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>납입기간 중 100만원, 납입기간 후 100만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 70만원, 납입기간 후 70만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>70만원</t>
         </is>
       </c>
       <c r="H379" t="n">
-        <v>8633</v>
+        <v>22336</v>
       </c>
       <c r="I379" t="n">
-        <v>21083</v>
+        <v>32772</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -18855,29 +18855,29 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)재가급여특약(월1회) 무배당</t>
+          <t>장기요양(1-5등급)시설급여특약(월1회) 무배당</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘시설급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
+          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘재가급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>납입기간 중 70만원, 납입기간 후 70만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 100만원, 납입기간 후 100만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>70만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="H380" t="n">
-        <v>22336</v>
+        <v>8633</v>
       </c>
       <c r="I380" t="n">
-        <v>32772</v>
+        <v>21083</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -18946,34 +18946,34 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>치매(CDR1점이상)보장특약 무배당</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 치매보장개시일 이후에 ‘경도이상 치매상태’로 진단 확정되었을 경우(최초 1회한)</t>
+          <t>보험기간 중 피보험자가 사망한 경우</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>납입기간 중 1,000만원, 납입기간 후 1,000만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 10,000만원, 납입기간 후 10,000만원 + 증액계약의 사망보험금액</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="H382" t="n">
-        <v>2542</v>
+        <v>30917</v>
       </c>
       <c r="I382" t="n">
-        <v>2517</v>
+        <v>29667</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -18994,34 +18994,34 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>치매(CDR1점이상)보장특약 무배당</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 사망한 경우</t>
+          <t>보험기간 중 피보험자가 치매보장개시일 이후에 ‘경도이상 치매상태’로 진단 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>납입기간 중 10,000만원, 납입기간 후 10,000만원 + 증액계약의 사망보험금액</t>
+          <t>납입기간 중 1,000만원, 납입기간 후 1,000만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H383" t="n">
-        <v>30917</v>
+        <v>2542</v>
       </c>
       <c r="I383" t="n">
-        <v>29667</v>
+        <v>2517</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -19047,29 +19047,29 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)시설급여특약(월1회) 무배당</t>
+          <t>치매(CDR2점이상)보장특약 무배당</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘재가급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
+          <t>보험기간 중 피보험자가 치매보장개시일 이후에 ‘중등도이상 치매상태’로 진단 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>납입기간 중 100만원, 납입기간 후 100만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 1,000만원, 납입기간 후 1,000만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>1,000만원</t>
         </is>
       </c>
       <c r="H384" t="n">
-        <v>4683</v>
+        <v>2325</v>
       </c>
       <c r="I384" t="n">
-        <v>11442</v>
+        <v>2283</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
@@ -19095,29 +19095,29 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>장기요양(1-5등급)재가급여특약(월1회) 무배당</t>
+          <t>장기요양(1-5등급)시설급여특약(월1회) 무배당</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘시설급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
+          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘재가급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>납입기간 중 70만원, 납입기간 후 70만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 100만원, 납입기간 후 100만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>70만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="H385" t="n">
-        <v>12116</v>
+        <v>4683</v>
       </c>
       <c r="I385" t="n">
-        <v>17780</v>
+        <v>11442</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -19143,29 +19143,29 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>치매(CDR2점이상)보장특약 무배당</t>
+          <t>장기요양(1-5등급)재가급여특약(월1회) 무배당</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>보험기간 중 피보험자가 치매보장개시일 이후에 ‘중등도이상 치매상태’로 진단 확정되었을 경우(최초 1회한)</t>
+          <t>피보험자가 보험기간 중 장기요양보장개시일 이후에 ‘1~5등급 장기요양상태’로 판정받고 보험기간 중 ‘시설급여’를 이용하였을 경우(이용 1회당, 월간 1회한)</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>납입기간 중 1,000만원, 납입기간 후 1,000만원 + 증액계약의 보장보험금액</t>
+          <t>납입기간 중 70만원, 납입기간 후 70만원 + 증액계약의 보장보험금액</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>1,000만원</t>
+          <t>70만원</t>
         </is>
       </c>
       <c r="H386" t="n">
-        <v>2325</v>
+        <v>12116</v>
       </c>
       <c r="I386" t="n">
-        <v>2283</v>
+        <v>17780</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -19515,12 +19515,12 @@
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상,90일이상)</t>
+          <t>장기요양진단비(1-4등급)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
+          <t>노인장기요양보험 1-4등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-4등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F395" t="inlineStr"/>
@@ -19547,17 +19547,17 @@
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비(CDR2점이상,90일이상)</t>
+          <t>장기요양진단비(1-3등급)</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
+          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
+          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
         </is>
       </c>
       <c r="G396" t="inlineStr"/>
@@ -19583,15 +19583,19 @@
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>장기요양진단비(1-4등급)</t>
+          <t>중등도이상치매진단비(CDR2점이상,90일이상)</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>노인장기요양보험 1-4등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-4등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr"/>
+          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
+        </is>
+      </c>
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
@@ -19615,19 +19619,15 @@
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>장기요양진단비(1-3등급)</t>
+          <t>중증치매진단비(CDR3점이상,90일이상)</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
-        </is>
-      </c>
+          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
@@ -19699,12 +19699,12 @@
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상,90일이상)</t>
+          <t>장기요양진단비(1-4등급)</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
+          <t>노인장기요양보험 1-4등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-4등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -19731,17 +19731,17 @@
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비(CDR2점이상,90일이상)</t>
+          <t>장기요양진단비(1-3등급)</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
+          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
+          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
         </is>
       </c>
       <c r="G401" t="inlineStr"/>
@@ -19767,12 +19767,12 @@
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>장기요양진단비(1-4등급)</t>
+          <t>중증치매진단비(CDR3점이상,90일이상)</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>노인장기요양보험 1-4등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-4등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
+          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
@@ -19799,17 +19799,17 @@
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>장기요양진단비(1-3등급)</t>
+          <t>중등도이상치매진단비(CDR2점이상,90일이상)</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
+          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
         </is>
       </c>
       <c r="G403" t="inlineStr"/>
@@ -20067,15 +20067,19 @@
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상,90일이상)(간편)</t>
+          <t>중등도이상치매진단비(CDR2점이상,90일이상)(간편)</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr"/>
+          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
+        </is>
+      </c>
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
@@ -20099,19 +20103,15 @@
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비(CDR2점이상,90일이상)(간편)</t>
+          <t>중증치매진단비(CDR3점이상,90일이상)(간편)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
-        </is>
-      </c>
+          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
@@ -20251,19 +20251,15 @@
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>중등도이상치매진단비(CDR2점이상,90일이상)(간편)</t>
+          <t>중증치매진단비(CDR3점이상,90일이상)(간편)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
-        </is>
-      </c>
+          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
@@ -20287,17 +20283,17 @@
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>장기요양진단비(1-3등급)(간편)</t>
+          <t>중등도이상치매진단비(CDR2점이상,90일이상)(간편)</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
+          <t>보장개시일 이후 약관에서 정한 '중등도이상치매상태'로 진단확정시(최초1회한)</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+          <t>보험가입금액(질병이 원인인 경우 가입 후 1년간 보장 제외)</t>
         </is>
       </c>
       <c r="G416" t="inlineStr"/>
@@ -20355,15 +20351,19 @@
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상,90일이상)(간편)</t>
+          <t>장기요양진단비(1-3등급)(간편)</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>보장개시일 이후 약관에서 정한 '중증치매상태'로 진단확정시(최초1회한)</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr"/>
+          <t>노인장기요양보험 1-3등급 수급대상으로 인정(국민건강보험공단 등급판정위원회에 의하여 1-3등급의 장기요양등급을 판정)받은 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>보험가입금액(질병이 원인인 경우 계약일부터 경과기간 1년 미만시 보험가입금액의 50%)</t>
+        </is>
+      </c>
       <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
@@ -20435,17 +20435,17 @@
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>보험료납입면제대상(간편맞춤고지)</t>
+          <t>항암방사선치료Ⅱ(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="G420" t="inlineStr"/>
@@ -20503,17 +20503,17 @@
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>항암방사선치료Ⅱ(간편맞춤고지)</t>
+          <t>보험료납입면제대상(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
+          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>3천만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G422" t="inlineStr"/>
@@ -20539,17 +20539,17 @@
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>케어더블암치매진단(간편맞춤고지)</t>
+          <t>암진단Ⅱ(유사암제외)(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
+          <t>보장개시일 이후 ‘암’(‘유사암’제외)으로 진단 확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>5천만원</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="G423" t="inlineStr"/>
@@ -20575,17 +20575,17 @@
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>암진단Ⅱ(유사암제외)(간편맞춤고지)</t>
+          <t>케어더블암치매진단(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>보장개시일 이후 ‘암’(‘유사암’제외)으로 진단 확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>1천만원</t>
+          <t>5천만원</t>
         </is>
       </c>
       <c r="G424" t="inlineStr"/>
@@ -20659,15 +20659,19 @@
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>항암약물치료Ⅱ(간편맞춤고지)</t>
+          <t>케어더블암치매진단(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암약물치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암약물치료를 받은 경우 지급액의 20%</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
+          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>5천만원</t>
+        </is>
+      </c>
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr"/>
@@ -20691,17 +20695,17 @@
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>항암방사선치료Ⅱ(간편맞춤고지)</t>
+          <t>보험료납입면제대상(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
+          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>3천만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G427" t="inlineStr"/>
@@ -20763,17 +20767,17 @@
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>보험료납입면제대상(간편맞춤고지)</t>
+          <t>항암방사선치료Ⅱ(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="G429" t="inlineStr"/>
@@ -20799,19 +20803,15 @@
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>케어더블암치매진단(간편맞춤고지)</t>
+          <t>항암약물치료Ⅱ(간편맞춤고지)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>5천만원</t>
-        </is>
-      </c>
+          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암약물치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암약물치료를 받은 경우 지급액의 20%</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr"/>
@@ -20883,17 +20883,17 @@
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>보험료납입면제대상</t>
+          <t>암진단Ⅱ(유사암제외)</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>보장개시일 이후 ‘암’(‘유사암’제외)으로 진단 확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="G432" t="inlineStr"/>
@@ -20951,17 +20951,17 @@
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>암진단Ⅱ(유사암제외)</t>
+          <t>보험료납입면제대상</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>보장개시일 이후 ‘암’(‘유사암’제외)으로 진단 확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>1천만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G434" t="inlineStr"/>
@@ -20987,17 +20987,17 @@
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>항암방사선치료Ⅱ</t>
+          <t>케어더블암치매진단</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
+          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>3천만원</t>
+          <t>5천만원</t>
         </is>
       </c>
       <c r="G435" t="inlineStr"/>
@@ -21023,17 +21023,17 @@
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>케어더블암치매진단</t>
+          <t>항암방사선치료Ⅱ</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
+          <t>보장개시일 이후 암(유사암 제외)으로 진단 확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 100%기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단확정되고, 그 치료를 직접적인 목적으로 항암방사선치료를 받은 경우 지급액의 20%</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>5천만원</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="G436" t="inlineStr"/>
@@ -21107,17 +21107,17 @@
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>케어더블암치매진단</t>
+          <t>보험료납입면제대상</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
+          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>5천만원</t>
+          <t>100만원</t>
         </is>
       </c>
       <c r="G438" t="inlineStr"/>
@@ -21179,17 +21179,17 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>보험료납입면제대상</t>
+          <t>케어더블암치매진단</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되거나 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정된 경우※유사암 : 기타피부암, 갑상선암, 제자리암, 경계성종양</t>
+          <t>중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 되지 않고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 100%중증치매보장개시일 이후 ‘중증치매상태’로 진단확정되고, 암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정된 경우 지급액의 200%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되지 않고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 100%암보장개시일 이후 ‘암’(‘유사암’제외)으로 진단확정되고 중증치매보장개시일 이후 ‘중증치매상태’로 진단확정 된 경우 지급액의 200%</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>5천만원</t>
         </is>
       </c>
       <c r="G440" t="inlineStr"/>
@@ -21335,12 +21335,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>(무)경증이상장기요양재가급여특약(기본형)</t>
+          <t>(무)중증이상장기요양시설입소특약(기본형)</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -21354,10 +21354,10 @@
         </is>
       </c>
       <c r="H444" t="n">
-        <v>422</v>
+        <v>41</v>
       </c>
       <c r="I444" t="n">
-        <v>719</v>
+        <v>96</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -21383,12 +21383,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>(무)경증이상장기요양시설입소특약(기본형)</t>
+          <t>(무)중증이상장기요양재가급여특약(기본형)</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -21402,10 +21402,10 @@
         </is>
       </c>
       <c r="H445" t="n">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="I445" t="n">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -21431,12 +21431,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>(무)중증이상장기요양재가급여특약(기본형)</t>
+          <t>(무)경증이상장기요양시설입소특약(기본형)</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -21450,10 +21450,10 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="I446" t="n">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="J446" t="inlineStr">
         <is>
@@ -21479,12 +21479,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>(무)중증이상장기요양시설입소특약(기본형)</t>
+          <t>(무)경증이상장기요양재가급여특약(기본형)</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -21498,10 +21498,10 @@
         </is>
       </c>
       <c r="H447" t="n">
-        <v>41</v>
+        <v>422</v>
       </c>
       <c r="I447" t="n">
-        <v>96</v>
+        <v>719</v>
       </c>
       <c r="J447" t="inlineStr">
         <is>
@@ -21623,12 +21623,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>(무)경증이상장기요양시설입소특약(기본형)(해약환급금 미지급형V2)</t>
+          <t>(무)중증이상장기요양재가급여특약(기본형)(해약환급금 미지급형V2)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -21642,10 +21642,10 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="I450" t="n">
-        <v>245</v>
+        <v>67</v>
       </c>
       <c r="J450" t="inlineStr">
         <is>
@@ -21671,12 +21671,12 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>(무)중증이상장기요양재가급여특약(기본형)(해약환급금 미지급형V2)</t>
+          <t>(무)경증이상장기요양시설입소특약(기본형)(해약환급금 미지급형V2)</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -21690,10 +21690,10 @@
         </is>
       </c>
       <c r="H451" t="n">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="I451" t="n">
-        <v>67</v>
+        <v>245</v>
       </c>
       <c r="J451" t="inlineStr">
         <is>
@@ -21762,34 +21762,34 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>특약</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>(무)중증이상장기요양재가급여특약(기본형)(해약환급금 일부지급형)</t>
+          <t>사망보험금</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>피보험자가 보험기간 중 보장 개시일 이후에 재해를 원인으 로 사망하였을 때</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>이용 1회당 10만원</t>
+          <t>5년미만 500% , 5년이후 100%</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>10만원</t>
+          <t>10,000만원</t>
         </is>
       </c>
       <c r="H453" t="n">
-        <v>46</v>
+        <v>9167</v>
       </c>
       <c r="I453" t="n">
-        <v>76</v>
+        <v>7417</v>
       </c>
       <c r="J453" t="inlineStr">
         <is>
@@ -21810,34 +21810,34 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>주계약</t>
+          <t>특약</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>사망보험금</t>
+          <t>(무)경증이상장기요양재가급여특약(기본형)(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중 보장 개시일 이후에 재해를 원인으 로 사망하였을 때</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>5년미만 500% , 5년이후 100%</t>
+          <t>이용 1회당 10만원</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>10,000만원</t>
+          <t>10만원</t>
         </is>
       </c>
       <c r="H454" t="n">
-        <v>9167</v>
+        <v>380</v>
       </c>
       <c r="I454" t="n">
-        <v>7417</v>
+        <v>647</v>
       </c>
       <c r="J454" t="inlineStr">
         <is>
@@ -21863,12 +21863,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>(무)경증이상장기요양재가급여특약(기본형)(해약환급금 일부지급형)</t>
+          <t>(무)경증이상장기요양시설입소특약(기본형)(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -21882,10 +21882,10 @@
         </is>
       </c>
       <c r="H455" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="I455" t="n">
-        <v>647</v>
+        <v>279</v>
       </c>
       <c r="J455" t="inlineStr">
         <is>
@@ -21911,12 +21911,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>(무)경증이상장기요양시설입소특약(기본형)(해약환급금 일부지급형)</t>
+          <t>(무)중증이상장기요양재가급여특약(기본형)(해약환급금 일부지급형)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~5등급 으로 인한 시설급여"를 이용한 경우(다만 월1회 한도)</t>
+          <t>보험기간중 "장기요양상태보장개시일" 이후에 피보험자가 "노인장기요양보험 1~2등급 으로 인한 재가급여"를 이용한 경우(다만 월1회 한도)</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="I456" t="n">
-        <v>279</v>
+        <v>76</v>
       </c>
       <c r="J456" t="inlineStr">
         <is>
@@ -22227,12 +22227,12 @@
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
-          <t>파킨슨병진단비</t>
+          <t>중증치매진단비(CDR3점이상)</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>파킨슨병으로 진단 확정되었을 경우</t>
+          <t>중증치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -22259,12 +22259,12 @@
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)</t>
+          <t>파킨슨병진단비</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>중증치매상태로 진단 확정되었을 경우</t>
+          <t>파킨슨병으로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -22403,12 +22403,12 @@
       <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
-          <t>파킨슨병진단비(간편가입)</t>
+          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>파킨슨병으로 진단 확정되었을 경우</t>
+          <t>보장개시일 이후에 중등도이상치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -22435,12 +22435,12 @@
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
+          <t>중증알츠하이머치매진단비(간편가입)</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>중증치매상태로 진단 확정되었을 경우</t>
+          <t>중증알츠하이머치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -22467,12 +22467,12 @@
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비(간편가입)</t>
+          <t>파킨슨병진단비(간편가입)</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매상태로 진단 확정되었을 경우</t>
+          <t>파킨슨병으로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -22499,12 +22499,12 @@
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
+          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>보장개시일 이후에 중등도이상치매상태로 진단 확정되었을 경우</t>
+          <t>중증치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -22579,12 +22579,12 @@
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>파킨슨병진단비(간편가입)</t>
+          <t>중증알츠하이머치매진단비(간편가입)</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>파킨슨병으로 진단 확정되었을 경우</t>
+          <t>중증알츠하이머치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -22611,12 +22611,12 @@
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
+          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>중증치매상태로 진단 확정되었을 경우</t>
+          <t>보장개시일 이후에 중등도이상치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -22643,12 +22643,12 @@
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비(간편가입)</t>
+          <t>파킨슨병진단비(간편가입)</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매상태로 진단 확정되었을 경우</t>
+          <t>파킨슨병으로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -22675,12 +22675,12 @@
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
+          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>보장개시일 이후에 중등도이상치매상태로 진단 확정되었을 경우</t>
+          <t>중증치매상태로 진단 확정되었을 경우</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -22755,12 +22755,12 @@
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~2등급)</t>
+          <t>중증치매진단비(CDR3점이상)</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -22787,12 +22787,12 @@
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~4등급)</t>
+          <t>중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -22851,12 +22851,12 @@
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)</t>
+          <t>장기요양등급진단비(1~4등급)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
+          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -22883,12 +22883,12 @@
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비</t>
+          <t>장기요양등급진단비(1~2등급)</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -22963,12 +22963,12 @@
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)</t>
+          <t>장기요양등급진단비(1~4등급)</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
+          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -22995,12 +22995,12 @@
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비</t>
+          <t>장기요양등급진단비(1~2등급)</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -23059,12 +23059,12 @@
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~4등급)</t>
+          <t>중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -23091,12 +23091,12 @@
       <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~2등급)</t>
+          <t>중증치매진단비(CDR3점이상)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -23171,12 +23171,12 @@
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비</t>
+          <t>중등도치매진단비(CDR2점이상)</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -23203,12 +23203,12 @@
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
-          <t>중등도치매진단비(CDR2점이상)</t>
+          <t>중증치매진단비(CDR3점이상)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -23235,12 +23235,12 @@
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~4등급)</t>
+          <t>중증알츠하이머치매진단비</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -23267,12 +23267,12 @@
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~2등급)</t>
+          <t>장기요양등급진단비(1~4등급)</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -23299,12 +23299,12 @@
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)</t>
+          <t>장기요양등급진단비(1~2등급)</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
+          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -23411,12 +23411,12 @@
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~4등급)(경증간편가입)</t>
+          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -23443,12 +23443,12 @@
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~2등급)(경증간편가입)</t>
+          <t>중증알츠하이머치매진단비(간편가입)</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -23475,12 +23475,12 @@
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비(간편가입)</t>
+          <t>장기요양등급진단비(1~4등급)(경증간편가입)</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -23507,12 +23507,12 @@
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
+          <t>장기요양등급진단비(1~2등급)(경증간편가입)</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
+          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -23587,12 +23587,12 @@
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~2등급)(경증간편가입)</t>
+          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -23619,12 +23619,12 @@
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>장기요양등급진단비(1~4등급)(경증간편가입)</t>
+          <t>중증알츠하이머치매진단비(간편가입)</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -23651,12 +23651,12 @@
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>중증치매진단비(CDR3점이상)(간편가입)</t>
+          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증치매상태로 진단시(최초 1회한)</t>
+          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -23683,12 +23683,12 @@
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비(간편가입)</t>
+          <t>장기요양등급진단비(1~4등급)(경증간편가입)</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>“1~4등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -23715,12 +23715,12 @@
       <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr">
         <is>
-          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
+          <t>장기요양등급진단비(1~2등급)(경증간편가입)</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
+          <t>“1~2등급의 장기요양등급” 판정시 (최초 1회한)</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -24243,12 +24243,12 @@
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr">
         <is>
-          <t>중증알츠하이머치매진단비(간편가입)</t>
+          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
+          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -24275,12 +24275,12 @@
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr">
         <is>
-          <t>중등도치매진단비(CDR2점이상)(간편가입)</t>
+          <t>중증알츠하이머치매진단비(간편가입)</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>보장개시일 이후 상해 또는 질병으로 인해 중등도이상치매상태로 진단시(최초 1회한)</t>
+          <t>상해 또는 질병으로 인해 중증알츠하이머치매상태로 진단시(최초 1회한)</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
